--- a/Mask資料.xlsx
+++ b/Mask資料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s-katsuhiro.ando\Desktop\アルバック様\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6ACBEF-E746-4596-AFC5-B163922F13D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B50653C-E957-4944-B934-CBE6C20FC1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-11175" windowWidth="29040" windowHeight="15720" xr2:uid="{1A1092B3-8E67-437E-8B65-EB95A875E335}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
   <si>
     <t>各名称と処理の流れ。</t>
     <rPh sb="4" eb="6">
@@ -67,38 +67,6 @@
     <t>IPC（CTC側）</t>
     <rPh sb="7" eb="8">
       <t>ガワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>制御装置が出力するデータ（SMPLING、EVENT、PROCESS）をLogManagerがファイルにして特定のフォルダに格納する</t>
-    <rPh sb="0" eb="4">
-      <t>セイギョソウチ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>カクノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>各ファイルが格納されるフォルダとファイル名は特定されている</t>
-    <rPh sb="0" eb="1">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カクノウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>トクテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -107,23 +75,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>.\SamplingLog\&lt;Chamber&gt;\</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>yyyyMMdd_HHmm.csv</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>EVENT</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>.\EventLog\&lt;接続先&gt;\</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>yyyyMMdd_HH.evt</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -131,66 +83,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>.\ProcessLog\</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>yyyyMMdd_HHmmss.log</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>[C]の送信状態と履歴をSQLiteに登録する</t>
-    <rPh sb="4" eb="8">
-      <t>ソウシンジョウタイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>リレキ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>[C]の送信状況ログを出力する</t>
-    <rPh sb="4" eb="6">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>[C]の処理時のOS状態を測定出力する</t>
-    <rPh sb="4" eb="7">
-      <t>ショリジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ソクテイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>DataServer側</t>
     <rPh sb="10" eb="11">
       <t>ガワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>[G]の受信状態をSQLiteに登録する</t>
-    <rPh sb="16" eb="18">
-      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -208,22 +103,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>[H]の処理時のOS状態を測定出力する</t>
-    <rPh sb="4" eb="7">
-      <t>ショリジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ソクテイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ログデータを登録　SAMPLINGはInfluxDBに、EVENT、PROCESSはPostgreSQLに それぞれ登録する</t>
     <rPh sb="58" eb="60">
       <t>トウロク</t>
@@ -241,30 +120,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>確認</t>
-    <rPh sb="0" eb="2">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Serilogからのログとは、お客様PCで取得するログファイル</t>
-    <rPh sb="16" eb="18">
-      <t>キャクサマ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>例えば</t>
-    <rPh sb="0" eb="1">
-      <t>タト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>イレギュラーケース時の動作確認</t>
     <rPh sb="9" eb="10">
       <t>ジ</t>
@@ -276,170 +131,6 @@
   </si>
   <si>
     <t>アルバック様PC</t>
-  </si>
-  <si>
-    <t>ある装置の動作ログをファイルとして出力し、それをZZAgent(Sender側)が取得する。取得したファイルをZZAgent(Reciver側)に送信してその送信時の状態・状況をSQLiteに登録し、OSの各状態を取得記録。その作業の一連をログに記録する。</t>
-    <rPh sb="2" eb="4">
-      <t>ソウチ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ドウサ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>ガワ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="81" eb="82">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="86" eb="88">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="92" eb="98">
-      <t>イテニトウロク</t>
-    </rPh>
-    <rPh sb="103" eb="106">
-      <t>カクジョウタイ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>キロク</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>イチレン</t>
-    </rPh>
-    <rPh sb="123" eb="125">
-      <t>キロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>また、ZZAgent(Sender側)では受信したファイルをSQLiteに登録し、OSの各状態を取得記録。その作業の一連をログに記録する。</t>
-    <rPh sb="21" eb="23">
-      <t>ジュシン</t>
-    </rPh>
-    <rPh sb="33" eb="39">
-      <t>イテニトウロク</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>キロク</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>イチレン</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>キロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ZZsightではSQLiteに登録されたデータを画面に表示されることと、その際のOSの各状態を取得記録する。</t>
-    <rPh sb="12" eb="18">
-      <t>イテニトウロク</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="44" eb="47">
-      <t>カクジョウタイ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>キロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>[A]により特定のフォルダにファイルが格納されると、SenderがZZAgentディレクトリをスキャンし、送信対象ファイルを検出する</t>
-    <rPh sb="6" eb="8">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>カクノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>[B]で取得したファイルを、TLSありgRPC Bidirectional StreamingによりZZAgent SenderからZZAgent Receiverへ送信する。ReceiverはSenderへStartFileAck、ChunkAck、TransferResZZtを応答する。</t>
-  </si>
-  <si>
-    <t>ZZAgent Sender送信されたファイルをZZAgent Reciverで受信する</t>
-    <rPh sb="14" eb="16">
-      <t>ソウシン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ジュシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ZZsightのOS状態を測定出力する</t>
-    <rPh sb="10" eb="12">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ソクテイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Sender側　C:\CTC-Main\Log\ZZAgent.Sender\ZZAgent.Sender-yyyyMMdd.log</t>
-    <rPh sb="6" eb="7">
-      <t>ガワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Reciver側　D:\DataServer-Main\Log\ZZAgent.Receiver\ZZAgent.Receiver-yyyyMMdd.log</t>
-    <rPh sb="7" eb="8">
-      <t>ガワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>■■■ ZZAgentディレクトリ ■■■</t>
@@ -452,6 +143,371 @@
   </si>
   <si>
     <t>BINの親ディレクトリをルートディレクトリとする BINは ZZAgent.Sender.exe が格納されているフォルダ</t>
+  </si>
+  <si>
+    <t>※ZZAgentディレクトリ＝C:\CTC-main\ZZAgent\</t>
+  </si>
+  <si>
+    <t>C:\CTC-main\ZZAgent\SamplingLog\Chamber1\yyyyMMdd_HHmm.csv</t>
+  </si>
+  <si>
+    <t>C:\CTC-main\ZZAgent\SamplingLog\Chamber2\yyyyMMdd_HHmm.csv</t>
+  </si>
+  <si>
+    <t>C:\CTC-main\ZZAgent\SamplingLog\Chamber3\yyyyMMdd_HHmm.csv</t>
+  </si>
+  <si>
+    <t>C:\CTC-main\ZZAgent\EventLog\PMC\yyyyMMdd_HH.evt</t>
+  </si>
+  <si>
+    <t>C:\CTC-main\ZZAgent\EventLog\TMC\yyyyMMdd_HH.evt</t>
+  </si>
+  <si>
+    <t>C:\CTC-main\ZZAgent\EventLog\CTC\yyyyMMdd_HH.evt</t>
+  </si>
+  <si>
+    <t>C:\CTC-main\ZZAgent\ProcessLog\yyyyMMdd_HHmmss.log</t>
+  </si>
+  <si>
+    <t>10分間隔で格納される</t>
+    <rPh sb="2" eb="3">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1時間間隔で格納される</t>
+    <rPh sb="1" eb="3">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1秒間隔で格納される</t>
+    <rPh sb="1" eb="4">
+      <t>ビョウカンカク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※格納されるデータがない場合、ファイルは生成されない</t>
+    <rPh sb="1" eb="3">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイルとして出力された装置の動作ログがZZAgent-Sender経由でZZAgent-Reciverに転送される。</t>
+    <rPh sb="7" eb="9">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソウチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ケイユ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>制御装置が出力するデータ（SMPLING、EVENT、PROCESS）を</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LogManager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>がファイルにして特定のフォルダに格納する</t>
+    </r>
+    <rPh sb="0" eb="4">
+      <t>セイギョソウチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カクノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各ファイルが格納されるフォルダ名とファイル名</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[B]で取得したファイルを、TLSありgRPC通信によりZZAgent-SenderからZZAgent-Receiverへ送信する。ZZAgent-ReceiverはZZAgent-SenderへStartFileAck、ChunkAck、TransferResultを応答する。</t>
+    <rPh sb="23" eb="25">
+      <t>ツウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[C]の転送状況ログを出力する</t>
+    <rPh sb="4" eb="6">
+      <t>テンソウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[A]により特定のフォルダにファイルが格納されると、ZZAgent-Senderが60秒周期でZZAgentディレクトリをスキャンし、転送対象ファイルを検出する</t>
+    <rPh sb="6" eb="8">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>シュウキ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>テンソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ZZAgent-Sender転送されたファイルをZZAgent-Reciverで受信し、ZZsightのDBにデータを登録する</t>
+    <rPh sb="14" eb="16">
+      <t>テンソウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[G]の受信状況とDB登録状況をSQLiteに登録する</t>
+    <rPh sb="6" eb="8">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>転送時の状況をZZAgent-Sender側のSQLiteに登録し、OSリソースの各状況も取得記録。その作業の一連をZZAgent-Senderのログに記録する。</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[C]の転送状況と履歴をSQLiteに登録する</t>
+    <rPh sb="4" eb="6">
+      <t>テンソウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[C]の処理時のOSリソース状態を測定出力する</t>
+    <rPh sb="4" eb="7">
+      <t>ショリジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ソクテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[H]の処理時のOSリソース状態を測定出力する</t>
+    <rPh sb="4" eb="7">
+      <t>ショリジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ソクテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ZZsightのOSリソース状態を測定出力する</t>
+    <rPh sb="14" eb="16">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ソクテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>また、ZZAgent-Receiverでは受信したファイルをZZsightのDBに登録。その登録時の状況をZZAgent-Receiver側のSQLiteに登録し、OSリソース状態も取得記録。その作業の一連をZZAgent-Receiverのログに記録する。</t>
+    <rPh sb="21" eb="23">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="74" eb="80">
+      <t>イテニトウロク</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>イチレン</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ZZsightではSQLiteに登録されたデータを画面に表示されることと、その際のOSリソース状態を取得記録する。</t>
+    <rPh sb="12" eb="18">
+      <t>イテニトウロク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -560,7 +616,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="218378" cy="227671"/>
@@ -631,7 +687,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="218377" cy="227671"/>
@@ -702,7 +758,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="218378" cy="229575"/>
@@ -773,7 +829,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>227669</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="218377" cy="227671"/>
@@ -844,7 +900,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="218378" cy="227670"/>
@@ -915,7 +971,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="222189" cy="229576"/>
@@ -986,7 +1042,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="222189" cy="227670"/>
@@ -1057,7 +1113,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>227670</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="222189" cy="227670"/>
@@ -1128,7 +1184,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="222189" cy="227670"/>
@@ -1199,7 +1255,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="222189" cy="227670"/>
@@ -1270,7 +1326,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="222188" cy="227670"/>
@@ -1342,13 +1398,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>207305</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -1364,8 +1420,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="324971" y="19722353"/>
-          <a:ext cx="16808823" cy="5589938"/>
+          <a:off x="324971" y="21067059"/>
+          <a:ext cx="17021735" cy="5589938"/>
           <a:chOff x="309563" y="20955000"/>
           <a:chExt cx="16668750" cy="5926115"/>
         </a:xfrm>
@@ -3175,13 +3231,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>20730</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -3197,8 +3253,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="324971" y="12791626"/>
-          <a:ext cx="16808823" cy="5586021"/>
+          <a:off x="324971" y="14136332"/>
+          <a:ext cx="17021735" cy="5586021"/>
           <a:chOff x="309563" y="13590045"/>
           <a:chExt cx="16668750" cy="5936205"/>
         </a:xfrm>
@@ -4794,8 +4850,8 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>231319</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8667750" cy="925287"/>
     <xdr:sp macro="" textlink="">
@@ -4811,7 +4867,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8315325" y="8003719"/>
+          <a:off x="8572500" y="8348870"/>
           <a:ext cx="8667750" cy="925287"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4904,13 +4960,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>12511</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>221254</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>2535</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4980,13 +5036,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>208983</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>136634</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>209989</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -5002,8 +5058,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="100853" y="1333381"/>
-          <a:ext cx="13804000" cy="6044563"/>
+          <a:off x="100853" y="1557499"/>
+          <a:ext cx="14016912" cy="6044562"/>
           <a:chOff x="100853" y="1329571"/>
           <a:chExt cx="13807810" cy="6052183"/>
         </a:xfrm>
@@ -6155,11 +6211,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152DD4BE-1BCE-4BF0-996E-3B5D7332929E}">
-  <dimension ref="B1:AC122"/>
+  <dimension ref="B1:L128"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="1.296875" customWidth="1"/>
     <col min="2" max="2" width="2.8984375" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" customWidth="1"/>
+    <col min="10" max="10" width="10.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.45">
@@ -6174,193 +6232,213 @@
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C36" t="s">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="C37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="C39" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L39" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C37" t="s">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="D41" t="s">
+        <v>19</v>
+      </c>
+      <c r="L41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="C42" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C38" t="s">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="D44" t="s">
+        <v>22</v>
+      </c>
+      <c r="L44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="C45" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E38" t="s">
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="C47" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="C48" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C49" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C50" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C51" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H38" t="s">
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C55" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C57" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C39" t="s">
+    <row r="58" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C58" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C59" t="s">
         <v>8</v>
       </c>
-      <c r="E39" t="s">
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C60" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C63" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H39" t="s">
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C94" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C40" t="s">
+    <row r="123" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C123" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C124" t="s">
         <v>11</v>
       </c>
-      <c r="E40" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40" t="s">
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C125" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C41" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C43" t="s">
+    <row r="126" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C126" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C44" t="s">
+    <row r="127" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C127" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C49" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C50" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C51" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C52" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C53" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C54" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C57" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="AC58" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="AC59" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="AC60" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="AC61" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="AC62" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C88" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C117" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C118" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C119" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C120" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C121" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C122" s="5"/>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C128" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
